--- a/vlearn-app/public/quiz_excel/Day_14_AI Evaluation _ Benchmarking/Day_14_Phan_02_19_Cau.xlsx
+++ b/vlearn-app/public/quiz_excel/Day_14_AI Evaluation _ Benchmarking/Day_14_Phan_02_19_Cau.xlsx
@@ -805,7 +805,7 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
@@ -833,7 +833,7 @@
       <c r="J7" s="3" t="n"/>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Trừ chance agreement ở tử và chia cho dư địa còn lại.</t>
+          <t>Cohen's Kappa: κ = (p_o - p_e) / (1 - p_e) = (0,80 - 0,50) / (1 - 0,50) = 0,30 / 0,50 = 0,6.</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>1,2,3,4</t>
         </is>
       </c>
       <c r="I9" s="4" t="n">
@@ -936,7 +936,7 @@
       <c r="J9" s="3" t="n"/>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Mọi claim trong expected answer phải truy được về evidence nào?</t>
+          <t>Các trường bắt buộc để một ca kiểm thử trở thành golden record có thể kiểm toán: (a) Stable case ID bất biến, (b) câu hỏi và hành vi kỳ vọng được chuyên gia phê duyệt, (c) trích dẫn nguồn bằng chứng chính xác (provenance), (d) siêu dữ liệu về độ khó, mức độ rủi ro.</t>
         </is>
       </c>
     </row>
@@ -1078,7 +1078,7 @@
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>1,2,3,4</t>
         </is>
       </c>
       <c r="I12" s="4" t="n">
@@ -1087,7 +1087,7 @@
       <c r="J12" s="3" t="n"/>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Evidence nào cho biết model đã nhìn thấy case và case đã đổi ra sao?</t>
+          <t>Các biện pháp kiểm soát benchmark đáng tin cậy: (a) Duy trì ID ổn định và lịch sử thay đổi, (b) tách biệt tập public/dev với tập private held-out (để chống overfitting), (c) ghi nhận truy cập và tăng version khi cập nhật, (d) đưa các lỗi production đã xác nhận vào tập living test qua quy trình phê duyệt.</t>
         </is>
       </c>
     </row>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>1,2,3,4</t>
         </is>
       </c>
       <c r="I14" s="4" t="n">
@@ -1196,7 +1196,7 @@
       <c r="J14" s="3" t="n"/>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Filter đánh chất lượng/evidence của candidate, không chỉ acceptance rate.</t>
+          <t>Lý do hợp lệ để loại bỏ một câu hỏi sinh tự động (synthetic candidate): (a) Đáp án kỳ vọng không có căn cứ từ nguồn tài liệu, (b) câu hỏi thiếu dữ kiện để có đáp án duy nhất, (c) trùng lặp ngữ nghĩa với ca kiểm thử đã có, (d) chỉ đổi tên riêng mà không thay đổi bản chất tác vụ.</t>
         </is>
       </c>
     </row>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>25</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
@@ -1398,7 +1398,7 @@
       <c r="J18" s="3" t="n"/>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Chỉ đếm call thỏa đủ điều kiện redundant đã nêu.</t>
+          <t>Tỷ lệ redundant tool calls = (2 redundant calls / 8 total tool calls) * 100% = 25%.</t>
         </is>
       </c>
     </row>
